--- a/recueil_bon.xlsx
+++ b/recueil_bon.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/thomashusson/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/thomashusson/Documents/Projets/These_Brieuc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CABFB280-CE91-5B42-A874-55016A9C6805}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95D6A05A-3ED6-1E48-9D85-48A98D767837}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Recueil" sheetId="2" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="971" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1029" uniqueCount="140">
   <si>
     <t>oui</t>
   </si>
@@ -446,6 +446,15 @@
   </si>
   <si>
     <t>U2b_E1</t>
+  </si>
+  <si>
+    <t>Sexe</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>M</t>
   </si>
 </sst>
 </file>
@@ -529,11 +538,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Recueil" displayName="Recueil" ref="B1:Y55" totalsRowShown="0">
-  <autoFilter ref="B1:Y55" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
-  <tableColumns count="24">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Recueil" displayName="Recueil" ref="B1:Z55" totalsRowShown="0">
+  <autoFilter ref="B1:Z55" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
+  <tableColumns count="25">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Nom"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="prenom"/>
+    <tableColumn id="15" xr3:uid="{6CD0DB8D-F74D-924C-A394-41F573ABC2F5}" name="Sexe"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="DDN"/>
     <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Date_de_recueil"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Age" dataDxfId="0">
@@ -826,23 +836,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AK55"/>
+  <dimension ref="A1:AL55"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="13.33203125" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="13.83203125" customWidth="1"/>
-    <col min="5" max="5" width="17.5" customWidth="1"/>
-    <col min="6" max="7" width="11.5" customWidth="1"/>
-    <col min="8" max="8" width="15.1640625" customWidth="1"/>
-    <col min="9" max="9" width="11.5" customWidth="1"/>
-    <col min="10" max="11" width="16.5" customWidth="1"/>
-    <col min="12" max="12" width="11.5" customWidth="1"/>
-    <col min="13" max="17" width="12.5" customWidth="1"/>
-    <col min="18" max="18" width="11.5" customWidth="1"/>
+    <col min="3" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="13.83203125" customWidth="1"/>
+    <col min="6" max="6" width="17.5" customWidth="1"/>
+    <col min="7" max="8" width="11.5" customWidth="1"/>
+    <col min="9" max="9" width="15.1640625" customWidth="1"/>
+    <col min="10" max="10" width="11.5" customWidth="1"/>
+    <col min="11" max="12" width="16.5" customWidth="1"/>
+    <col min="13" max="13" width="11.5" customWidth="1"/>
+    <col min="14" max="18" width="12.5" customWidth="1"/>
+    <col min="19" max="19" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>120</v>
       </c>
@@ -853,73 +863,76 @@
         <v>121</v>
       </c>
       <c r="D1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E1" t="s">
         <v>5</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>122</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>134</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>57</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>123</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>124</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>125</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="R1" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="S1" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="T1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>129</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>130</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>131</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>132</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>133</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -929,26 +942,26 @@
       <c r="C2" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2" t="s">
+        <v>138</v>
+      </c>
+      <c r="E2" s="1">
         <v>28100</v>
       </c>
-      <c r="E2" s="1">
+      <c r="F2" s="1">
         <v>45572</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <f>INT((Recueil[[#This Row],[Date_de_recueil]]-Recueil[[#This Row],[DDN]])/365)</f>
         <v>47</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>16</v>
       </c>
-      <c r="I2" t="s">
-        <v>7</v>
-      </c>
       <c r="J2" t="s">
         <v>7</v>
       </c>
-      <c r="M2" t="s">
+      <c r="K2" t="s">
         <v>7</v>
       </c>
       <c r="N2" t="s">
@@ -964,11 +977,11 @@
         <v>7</v>
       </c>
       <c r="R2" t="s">
+        <v>7</v>
+      </c>
+      <c r="S2" t="s">
         <v>13</v>
       </c>
-      <c r="T2" t="s">
-        <v>7</v>
-      </c>
       <c r="U2" t="s">
         <v>7</v>
       </c>
@@ -979,10 +992,13 @@
         <v>7</v>
       </c>
       <c r="X2" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -992,48 +1008,48 @@
       <c r="C3" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D3" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3" s="1">
         <v>28397</v>
       </c>
-      <c r="E3" s="1">
+      <c r="F3" s="1">
         <v>45453</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <f>INT((Recueil[[#This Row],[Date_de_recueil]]-Recueil[[#This Row],[DDN]])/365)</f>
         <v>46</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>16</v>
       </c>
-      <c r="I3" t="s">
-        <v>7</v>
-      </c>
       <c r="J3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L3" t="s">
         <v>1</v>
       </c>
-      <c r="M3" t="s">
-        <v>8</v>
-      </c>
       <c r="N3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O3" t="s">
         <v>7</v>
       </c>
       <c r="P3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T3" t="s">
-        <v>7</v>
+        <v>7</v>
+      </c>
+      <c r="S3" t="s">
+        <v>8</v>
       </c>
       <c r="U3" t="s">
         <v>7</v>
@@ -1045,10 +1061,13 @@
         <v>7</v>
       </c>
       <c r="X3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+        <v>7</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1058,33 +1077,33 @@
       <c r="C4" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4" t="s">
+        <v>138</v>
+      </c>
+      <c r="E4" s="1">
         <v>26778</v>
       </c>
-      <c r="E4" s="1">
+      <c r="F4" s="1">
         <v>45572</v>
       </c>
-      <c r="F4">
+      <c r="G4">
         <f>INT((Recueil[[#This Row],[Date_de_recueil]]-Recueil[[#This Row],[DDN]])/365)</f>
         <v>51</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>17</v>
       </c>
-      <c r="I4" t="s">
-        <v>7</v>
-      </c>
       <c r="J4" t="s">
         <v>7</v>
       </c>
       <c r="K4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L4" t="s">
         <v>0</v>
       </c>
-      <c r="L4" t="s">
-        <v>8</v>
-      </c>
       <c r="M4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N4" t="s">
         <v>7</v>
@@ -1099,10 +1118,10 @@
         <v>7</v>
       </c>
       <c r="R4" t="s">
-        <v>8</v>
-      </c>
-      <c r="T4" t="s">
-        <v>7</v>
+        <v>7</v>
+      </c>
+      <c r="S4" t="s">
+        <v>8</v>
       </c>
       <c r="U4" t="s">
         <v>7</v>
@@ -1114,10 +1133,13 @@
         <v>7</v>
       </c>
       <c r="X4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+        <v>7</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1127,31 +1149,31 @@
       <c r="C5" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D5" t="s">
+        <v>138</v>
+      </c>
+      <c r="E5" s="1">
         <v>21806</v>
       </c>
-      <c r="E5" s="1">
+      <c r="F5" s="1">
         <v>45453</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <f>INT((Recueil[[#This Row],[Date_de_recueil]]-Recueil[[#This Row],[DDN]])/365)</f>
         <v>64</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>17</v>
       </c>
-      <c r="I5" t="s">
-        <v>7</v>
-      </c>
       <c r="J5" t="s">
         <v>7</v>
       </c>
       <c r="K5" t="s">
+        <v>7</v>
+      </c>
+      <c r="L5" t="s">
         <v>0</v>
       </c>
-      <c r="L5" t="s">
-        <v>7</v>
-      </c>
       <c r="M5" t="s">
         <v>7</v>
       </c>
@@ -1171,11 +1193,11 @@
         <v>7</v>
       </c>
       <c r="S5" t="s">
+        <v>7</v>
+      </c>
+      <c r="T5" t="s">
         <v>25</v>
       </c>
-      <c r="T5" t="s">
-        <v>7</v>
-      </c>
       <c r="U5" t="s">
         <v>7</v>
       </c>
@@ -1189,10 +1211,13 @@
         <v>7</v>
       </c>
       <c r="Y5" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1202,31 +1227,31 @@
       <c r="C6" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6" t="s">
+        <v>138</v>
+      </c>
+      <c r="E6" s="1">
         <v>27971</v>
       </c>
-      <c r="E6" s="1">
+      <c r="F6" s="1">
         <v>45600</v>
       </c>
-      <c r="F6">
+      <c r="G6">
         <f>INT((Recueil[[#This Row],[Date_de_recueil]]-Recueil[[#This Row],[DDN]])/365)</f>
         <v>48</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>16</v>
       </c>
-      <c r="I6" t="s">
-        <v>8</v>
-      </c>
       <c r="J6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K6" t="s">
+        <v>7</v>
+      </c>
+      <c r="L6" t="s">
         <v>0</v>
       </c>
-      <c r="L6" t="s">
-        <v>7</v>
-      </c>
       <c r="M6" t="s">
         <v>7</v>
       </c>
@@ -1240,17 +1265,17 @@
         <v>7</v>
       </c>
       <c r="Q6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S6" t="s">
+        <v>7</v>
+      </c>
+      <c r="T6" t="s">
         <v>25</v>
       </c>
-      <c r="T6" t="s">
-        <v>7</v>
-      </c>
       <c r="U6" t="s">
         <v>7</v>
       </c>
@@ -1264,10 +1289,13 @@
         <v>7</v>
       </c>
       <c r="Y6" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z6" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1277,33 +1305,33 @@
       <c r="C7" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="1">
+      <c r="D7" t="s">
+        <v>138</v>
+      </c>
+      <c r="E7" s="1">
         <v>31411</v>
       </c>
-      <c r="E7" s="1">
+      <c r="F7" s="1">
         <v>45579</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <f>INT((Recueil[[#This Row],[Date_de_recueil]]-Recueil[[#This Row],[DDN]])/365)</f>
         <v>38</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H7" t="s">
         <v>16</v>
       </c>
-      <c r="I7" t="s">
-        <v>7</v>
-      </c>
       <c r="J7" t="s">
         <v>7</v>
       </c>
-      <c r="M7" t="s">
+      <c r="K7" t="s">
         <v>7</v>
       </c>
       <c r="N7" t="s">
         <v>7</v>
       </c>
       <c r="O7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P7" t="s">
         <v>8</v>
@@ -1312,14 +1340,14 @@
         <v>8</v>
       </c>
       <c r="R7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S7" t="s">
+        <v>7</v>
+      </c>
+      <c r="T7" t="s">
         <v>24</v>
       </c>
-      <c r="T7" t="s">
-        <v>7</v>
-      </c>
       <c r="U7" t="s">
         <v>7</v>
       </c>
@@ -1333,10 +1361,13 @@
         <v>7</v>
       </c>
       <c r="Y7" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z7" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1346,26 +1377,26 @@
       <c r="C8" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D8" t="s">
+        <v>138</v>
+      </c>
+      <c r="E8" s="1">
         <v>25837</v>
       </c>
-      <c r="E8" s="1">
+      <c r="F8" s="1">
         <v>45572</v>
       </c>
-      <c r="F8">
+      <c r="G8">
         <f>INT((Recueil[[#This Row],[Date_de_recueil]]-Recueil[[#This Row],[DDN]])/365)</f>
         <v>54</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>17</v>
       </c>
-      <c r="I8" t="s">
-        <v>7</v>
-      </c>
       <c r="J8" t="s">
         <v>7</v>
       </c>
-      <c r="M8" t="s">
+      <c r="K8" t="s">
         <v>7</v>
       </c>
       <c r="N8" t="s">
@@ -1381,25 +1412,28 @@
         <v>7</v>
       </c>
       <c r="R8" t="s">
-        <v>8</v>
-      </c>
-      <c r="T8" t="s">
+        <v>7</v>
+      </c>
+      <c r="S8" t="s">
         <v>8</v>
       </c>
       <c r="U8" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V8" t="s">
         <v>7</v>
       </c>
       <c r="W8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X8" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Y8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1409,26 +1443,26 @@
       <c r="C9" t="s">
         <v>32</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D9" t="s">
+        <v>138</v>
+      </c>
+      <c r="E9" s="1">
         <v>25837</v>
       </c>
-      <c r="E9" s="1">
+      <c r="F9" s="1">
         <v>45572</v>
       </c>
-      <c r="F9">
+      <c r="G9">
         <f>INT((Recueil[[#This Row],[Date_de_recueil]]-Recueil[[#This Row],[DDN]])/365)</f>
         <v>54</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>16</v>
       </c>
-      <c r="I9" t="s">
-        <v>8</v>
-      </c>
       <c r="J9" t="s">
         <v>8</v>
       </c>
-      <c r="M9" t="s">
+      <c r="K9" t="s">
         <v>8</v>
       </c>
       <c r="N9" t="s">
@@ -1438,31 +1472,34 @@
         <v>8</v>
       </c>
       <c r="P9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R9" t="s">
         <v>8</v>
       </c>
-      <c r="T9" t="s">
-        <v>7</v>
+      <c r="S9" t="s">
+        <v>8</v>
       </c>
       <c r="U9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X9" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Y9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1472,45 +1509,45 @@
       <c r="C10" t="s">
         <v>34</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D10" t="s">
+        <v>139</v>
+      </c>
+      <c r="E10" s="1">
         <v>28160</v>
       </c>
-      <c r="E10" s="1">
+      <c r="F10" s="1">
         <v>45513</v>
       </c>
-      <c r="F10">
+      <c r="G10">
         <f>INT((Recueil[[#This Row],[Date_de_recueil]]-Recueil[[#This Row],[DDN]])/365)</f>
         <v>47</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
         <v>17</v>
       </c>
-      <c r="I10" t="s">
-        <v>7</v>
-      </c>
       <c r="J10" t="s">
         <v>7</v>
       </c>
-      <c r="M10" t="s">
+      <c r="K10" t="s">
         <v>7</v>
       </c>
       <c r="N10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O10" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P10" t="s">
         <v>7</v>
       </c>
       <c r="Q10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R10" t="s">
         <v>8</v>
       </c>
-      <c r="T10" t="s">
-        <v>7</v>
+      <c r="S10" t="s">
+        <v>8</v>
       </c>
       <c r="U10" t="s">
         <v>7</v>
@@ -1522,10 +1559,13 @@
         <v>7</v>
       </c>
       <c r="X10" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+        <v>7</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1535,45 +1575,45 @@
       <c r="C11" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="1">
+      <c r="D11" t="s">
+        <v>139</v>
+      </c>
+      <c r="E11" s="1">
         <v>28160</v>
       </c>
-      <c r="E11" s="1">
+      <c r="F11" s="1">
         <v>45513</v>
       </c>
-      <c r="F11">
+      <c r="G11">
         <f>INT((Recueil[[#This Row],[Date_de_recueil]]-Recueil[[#This Row],[DDN]])/365)</f>
         <v>47</v>
       </c>
-      <c r="G11" t="s">
+      <c r="H11" t="s">
         <v>16</v>
       </c>
-      <c r="I11" t="s">
-        <v>7</v>
-      </c>
       <c r="J11" t="s">
         <v>7</v>
       </c>
-      <c r="M11" t="s">
+      <c r="K11" t="s">
         <v>7</v>
       </c>
       <c r="N11" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O11" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P11" t="s">
         <v>7</v>
       </c>
       <c r="Q11" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R11" t="s">
         <v>8</v>
       </c>
-      <c r="T11" t="s">
-        <v>7</v>
+      <c r="S11" t="s">
+        <v>8</v>
       </c>
       <c r="U11" t="s">
         <v>7</v>
@@ -1588,10 +1628,13 @@
         <v>7</v>
       </c>
       <c r="Y11" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z11" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1601,31 +1644,31 @@
       <c r="C12" t="s">
         <v>36</v>
       </c>
-      <c r="D12" s="1">
+      <c r="D12" t="s">
+        <v>138</v>
+      </c>
+      <c r="E12" s="1">
         <v>32405</v>
       </c>
-      <c r="E12" s="1">
+      <c r="F12" s="1">
         <v>45508</v>
       </c>
-      <c r="F12">
+      <c r="G12">
         <f>INT((Recueil[[#This Row],[Date_de_recueil]]-Recueil[[#This Row],[DDN]])/365)</f>
         <v>35</v>
       </c>
-      <c r="G12" t="s">
+      <c r="H12" t="s">
         <v>17</v>
       </c>
-      <c r="I12" t="s">
-        <v>7</v>
-      </c>
       <c r="J12" t="s">
         <v>7</v>
       </c>
       <c r="K12" t="s">
+        <v>7</v>
+      </c>
+      <c r="L12" t="s">
         <v>1</v>
       </c>
-      <c r="M12" t="s">
-        <v>7</v>
-      </c>
       <c r="N12" t="s">
         <v>7</v>
       </c>
@@ -1636,28 +1679,31 @@
         <v>7</v>
       </c>
       <c r="Q12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R12" t="s">
         <v>8</v>
       </c>
-      <c r="T12" t="s">
-        <v>7</v>
+      <c r="S12" t="s">
+        <v>8</v>
       </c>
       <c r="U12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V12" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X12" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Y12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1667,26 +1713,26 @@
       <c r="C13" t="s">
         <v>38</v>
       </c>
-      <c r="D13" s="1">
+      <c r="D13" t="s">
+        <v>139</v>
+      </c>
+      <c r="E13" s="1">
         <v>24766</v>
       </c>
-      <c r="E13" s="1">
+      <c r="F13" s="1">
         <v>45460</v>
       </c>
-      <c r="F13">
+      <c r="G13">
         <f>INT((Recueil[[#This Row],[Date_de_recueil]]-Recueil[[#This Row],[DDN]])/365)</f>
         <v>56</v>
       </c>
-      <c r="G13" t="s">
+      <c r="H13" t="s">
         <v>17</v>
       </c>
-      <c r="I13" t="s">
-        <v>7</v>
-      </c>
       <c r="J13" t="s">
         <v>7</v>
       </c>
-      <c r="M13" t="s">
+      <c r="K13" t="s">
         <v>7</v>
       </c>
       <c r="N13" t="s">
@@ -1702,25 +1748,28 @@
         <v>7</v>
       </c>
       <c r="R13" t="s">
-        <v>8</v>
-      </c>
-      <c r="T13" t="s">
-        <v>7</v>
+        <v>7</v>
+      </c>
+      <c r="S13" t="s">
+        <v>8</v>
       </c>
       <c r="U13" t="s">
         <v>7</v>
       </c>
       <c r="V13" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W13" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X13" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+        <v>7</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1730,33 +1779,33 @@
       <c r="C14" t="s">
         <v>40</v>
       </c>
-      <c r="D14" s="1">
+      <c r="D14" t="s">
+        <v>138</v>
+      </c>
+      <c r="E14" s="1">
         <v>21945</v>
       </c>
-      <c r="E14" s="1">
+      <c r="F14" s="1">
         <v>45460</v>
       </c>
-      <c r="F14">
+      <c r="G14">
         <f>INT((Recueil[[#This Row],[Date_de_recueil]]-Recueil[[#This Row],[DDN]])/365)</f>
         <v>64</v>
       </c>
-      <c r="G14" t="s">
+      <c r="H14" t="s">
         <v>16</v>
       </c>
-      <c r="I14" t="s">
-        <v>7</v>
-      </c>
       <c r="J14" t="s">
         <v>7</v>
       </c>
-      <c r="M14" t="s">
+      <c r="K14" t="s">
         <v>7</v>
       </c>
       <c r="N14" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P14" t="s">
         <v>7</v>
@@ -1768,28 +1817,31 @@
         <v>7</v>
       </c>
       <c r="S14" t="s">
+        <v>7</v>
+      </c>
+      <c r="T14" t="s">
         <v>25</v>
       </c>
-      <c r="T14" t="s">
-        <v>7</v>
-      </c>
       <c r="U14" t="s">
         <v>7</v>
       </c>
       <c r="V14" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X14" t="s">
         <v>7</v>
       </c>
       <c r="Y14" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z14" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1799,36 +1851,36 @@
       <c r="C15" t="s">
         <v>42</v>
       </c>
-      <c r="D15" s="1">
+      <c r="D15" t="s">
+        <v>138</v>
+      </c>
+      <c r="E15" s="1">
         <v>21903</v>
       </c>
-      <c r="E15" s="1">
+      <c r="F15" s="1">
         <v>45628</v>
       </c>
-      <c r="F15">
+      <c r="G15">
         <f>INT((Recueil[[#This Row],[Date_de_recueil]]-Recueil[[#This Row],[DDN]])/365)</f>
         <v>65</v>
       </c>
-      <c r="G15" t="s">
+      <c r="H15" t="s">
         <v>16</v>
       </c>
-      <c r="I15" t="s">
-        <v>7</v>
-      </c>
       <c r="J15" t="s">
-        <v>8</v>
-      </c>
-      <c r="M15" t="s">
+        <v>7</v>
+      </c>
+      <c r="K15" t="s">
         <v>8</v>
       </c>
       <c r="N15" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O15" t="s">
         <v>7</v>
       </c>
       <c r="P15" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q15" t="s">
         <v>8</v>
@@ -1836,11 +1888,11 @@
       <c r="R15" t="s">
         <v>8</v>
       </c>
-      <c r="T15" t="s">
-        <v>7</v>
+      <c r="S15" t="s">
+        <v>8</v>
       </c>
       <c r="U15" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V15" t="s">
         <v>8</v>
@@ -1851,8 +1903,11 @@
       <c r="X15" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Y15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1862,57 +1917,60 @@
       <c r="C16" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="1">
+      <c r="D16" t="s">
+        <v>139</v>
+      </c>
+      <c r="E16" s="1">
         <v>30027</v>
       </c>
-      <c r="E16" s="1">
+      <c r="F16" s="1">
         <v>45583</v>
       </c>
-      <c r="F16">
+      <c r="G16">
         <f>INT((Recueil[[#This Row],[Date_de_recueil]]-Recueil[[#This Row],[DDN]])/365)</f>
         <v>42</v>
       </c>
-      <c r="G16" t="s">
+      <c r="H16" t="s">
         <v>16</v>
       </c>
-      <c r="I16" t="s">
-        <v>7</v>
-      </c>
       <c r="J16" t="s">
         <v>7</v>
       </c>
-      <c r="M16" t="s">
+      <c r="K16" t="s">
         <v>7</v>
       </c>
       <c r="N16" t="s">
         <v>7</v>
       </c>
       <c r="O16" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P16" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q16" t="s">
-        <v>8</v>
-      </c>
-      <c r="T16" t="s">
-        <v>7</v>
+        <v>7</v>
+      </c>
+      <c r="R16" t="s">
+        <v>8</v>
       </c>
       <c r="U16" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V16" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W16" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X16" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="17" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="Y16" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1922,31 +1980,31 @@
       <c r="C17" t="s">
         <v>46</v>
       </c>
-      <c r="D17" s="1">
+      <c r="D17" t="s">
+        <v>139</v>
+      </c>
+      <c r="E17" s="1">
         <v>24889</v>
       </c>
-      <c r="E17" s="1">
+      <c r="F17" s="1">
         <v>45460</v>
       </c>
-      <c r="F17">
+      <c r="G17">
         <f>INT((Recueil[[#This Row],[Date_de_recueil]]-Recueil[[#This Row],[DDN]])/365)</f>
         <v>56</v>
       </c>
-      <c r="G17" t="s">
+      <c r="H17" t="s">
         <v>16</v>
       </c>
-      <c r="I17" t="s">
-        <v>7</v>
-      </c>
       <c r="J17" t="s">
         <v>7</v>
       </c>
       <c r="K17" t="s">
+        <v>7</v>
+      </c>
+      <c r="L17" t="s">
         <v>0</v>
       </c>
-      <c r="L17" t="s">
-        <v>7</v>
-      </c>
       <c r="M17" t="s">
         <v>7</v>
       </c>
@@ -1960,17 +2018,17 @@
         <v>7</v>
       </c>
       <c r="Q17" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R17" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S17" t="s">
+        <v>7</v>
+      </c>
+      <c r="T17" t="s">
         <v>24</v>
       </c>
-      <c r="T17" t="s">
-        <v>7</v>
-      </c>
       <c r="U17" t="s">
         <v>7</v>
       </c>
@@ -1981,10 +2039,13 @@
         <v>7</v>
       </c>
       <c r="X17" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="18" spans="1:37" x14ac:dyDescent="0.2">
+        <v>7</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1994,30 +2055,30 @@
       <c r="C18" t="s">
         <v>48</v>
       </c>
-      <c r="D18" s="1">
+      <c r="D18" t="s">
+        <v>138</v>
+      </c>
+      <c r="E18" s="1">
         <v>32076</v>
       </c>
-      <c r="E18" s="1">
+      <c r="F18" s="1">
         <v>45439</v>
       </c>
-      <c r="F18">
+      <c r="G18">
         <f>INT((Recueil[[#This Row],[Date_de_recueil]]-Recueil[[#This Row],[DDN]])/365)</f>
         <v>36</v>
       </c>
-      <c r="G18" t="s">
+      <c r="H18" t="s">
         <v>17</v>
       </c>
-      <c r="I18" t="s">
-        <v>7</v>
-      </c>
       <c r="J18" t="s">
-        <v>8</v>
-      </c>
-      <c r="M18" t="s">
+        <v>7</v>
+      </c>
+      <c r="K18" t="s">
         <v>8</v>
       </c>
       <c r="N18" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O18" t="s">
         <v>7</v>
@@ -2029,10 +2090,10 @@
         <v>7</v>
       </c>
       <c r="R18" t="s">
-        <v>8</v>
-      </c>
-      <c r="T18" t="s">
-        <v>7</v>
+        <v>7</v>
+      </c>
+      <c r="S18" t="s">
+        <v>8</v>
       </c>
       <c r="U18" t="s">
         <v>7</v>
@@ -2044,10 +2105,13 @@
         <v>7</v>
       </c>
       <c r="X18" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19" spans="1:37" x14ac:dyDescent="0.2">
+        <v>7</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
@@ -2057,31 +2121,31 @@
       <c r="C19" t="s">
         <v>50</v>
       </c>
-      <c r="D19" s="1">
+      <c r="D19" t="s">
+        <v>138</v>
+      </c>
+      <c r="E19" s="1">
         <v>24117</v>
       </c>
-      <c r="E19" s="1">
+      <c r="F19" s="1">
         <v>45439</v>
       </c>
-      <c r="F19">
+      <c r="G19">
         <f>INT((Recueil[[#This Row],[Date_de_recueil]]-Recueil[[#This Row],[DDN]])/365)</f>
         <v>58</v>
       </c>
-      <c r="G19" t="s">
+      <c r="H19" t="s">
         <v>16</v>
       </c>
-      <c r="I19" t="s">
-        <v>7</v>
-      </c>
       <c r="J19" t="s">
         <v>7</v>
       </c>
       <c r="K19" t="s">
+        <v>7</v>
+      </c>
+      <c r="L19" t="s">
         <v>0</v>
       </c>
-      <c r="L19" t="s">
-        <v>7</v>
-      </c>
       <c r="M19" t="s">
         <v>7</v>
       </c>
@@ -2098,10 +2162,10 @@
         <v>7</v>
       </c>
       <c r="R19" t="s">
-        <v>8</v>
-      </c>
-      <c r="T19" t="s">
-        <v>7</v>
+        <v>7</v>
+      </c>
+      <c r="S19" t="s">
+        <v>8</v>
       </c>
       <c r="U19" t="s">
         <v>7</v>
@@ -2116,10 +2180,13 @@
         <v>7</v>
       </c>
       <c r="Y19" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z19" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2129,26 +2196,26 @@
       <c r="C20" t="s">
         <v>52</v>
       </c>
-      <c r="D20" s="1">
+      <c r="D20" t="s">
+        <v>138</v>
+      </c>
+      <c r="E20" s="1">
         <v>24616</v>
       </c>
-      <c r="E20" s="1">
+      <c r="F20" s="1">
         <v>45436</v>
       </c>
-      <c r="F20">
+      <c r="G20">
         <f>INT((Recueil[[#This Row],[Date_de_recueil]]-Recueil[[#This Row],[DDN]])/365)</f>
         <v>57</v>
       </c>
-      <c r="G20" t="s">
+      <c r="H20" t="s">
         <v>16</v>
       </c>
-      <c r="I20" t="s">
-        <v>7</v>
-      </c>
       <c r="J20" t="s">
         <v>7</v>
       </c>
-      <c r="M20" t="s">
+      <c r="K20" t="s">
         <v>7</v>
       </c>
       <c r="N20" t="s">
@@ -2161,17 +2228,17 @@
         <v>7</v>
       </c>
       <c r="Q20" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R20" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S20" t="s">
+        <v>7</v>
+      </c>
+      <c r="T20" t="s">
         <v>25</v>
       </c>
-      <c r="T20" t="s">
-        <v>7</v>
-      </c>
       <c r="U20" t="s">
         <v>7</v>
       </c>
@@ -2179,13 +2246,16 @@
         <v>7</v>
       </c>
       <c r="W20" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X20" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="21" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="Y20" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>20</v>
       </c>
@@ -2195,31 +2265,31 @@
       <c r="C21" t="s">
         <v>54</v>
       </c>
-      <c r="D21" s="1">
+      <c r="D21" t="s">
+        <v>138</v>
+      </c>
+      <c r="E21" s="1">
         <v>26928</v>
       </c>
-      <c r="E21" s="1">
+      <c r="F21" s="1">
         <v>45677</v>
       </c>
-      <c r="F21">
+      <c r="G21">
         <f>INT((Recueil[[#This Row],[Date_de_recueil]]-Recueil[[#This Row],[DDN]])/365)</f>
         <v>51</v>
       </c>
-      <c r="G21" t="s">
+      <c r="H21" t="s">
         <v>17</v>
       </c>
-      <c r="I21" t="s">
-        <v>7</v>
-      </c>
       <c r="J21" t="s">
         <v>7</v>
       </c>
       <c r="K21" t="s">
+        <v>7</v>
+      </c>
+      <c r="L21" t="s">
         <v>0</v>
       </c>
-      <c r="L21" t="s">
-        <v>7</v>
-      </c>
       <c r="M21" t="s">
         <v>7</v>
       </c>
@@ -2233,22 +2303,22 @@
         <v>7</v>
       </c>
       <c r="Q21" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R21" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S21" t="s">
+        <v>7</v>
+      </c>
+      <c r="T21" t="s">
         <v>24</v>
       </c>
-      <c r="T21" t="s">
-        <v>7</v>
-      </c>
       <c r="U21" t="s">
         <v>7</v>
       </c>
       <c r="V21" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W21" t="s">
         <v>8</v>
@@ -2256,8 +2326,11 @@
       <c r="X21" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="Y21" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>21</v>
       </c>
@@ -2267,29 +2340,29 @@
       <c r="C22" t="s">
         <v>56</v>
       </c>
-      <c r="D22" s="1">
+      <c r="D22" t="s">
+        <v>138</v>
+      </c>
+      <c r="E22" s="1">
         <v>18705</v>
       </c>
-      <c r="E22" s="1">
+      <c r="F22" s="1">
         <v>45670</v>
       </c>
-      <c r="F22">
+      <c r="G22">
         <f>INT((Recueil[[#This Row],[Date_de_recueil]]-Recueil[[#This Row],[DDN]])/365)</f>
         <v>73</v>
       </c>
-      <c r="G22" t="s">
+      <c r="H22" t="s">
         <v>17</v>
       </c>
-      <c r="H22" t="s">
+      <c r="I22" t="s">
         <v>63</v>
       </c>
-      <c r="I22" t="s">
-        <v>7</v>
-      </c>
       <c r="J22" t="s">
         <v>7</v>
       </c>
-      <c r="M22" t="s">
+      <c r="K22" t="s">
         <v>7</v>
       </c>
       <c r="N22" t="s">
@@ -2299,22 +2372,22 @@
         <v>7</v>
       </c>
       <c r="P22" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q22" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R22" t="s">
-        <v>8</v>
-      </c>
-      <c r="T22" t="s">
-        <v>7</v>
+        <v>7</v>
+      </c>
+      <c r="S22" t="s">
+        <v>8</v>
       </c>
       <c r="U22" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V22" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W22" t="s">
         <v>7</v>
@@ -2323,10 +2396,13 @@
         <v>7</v>
       </c>
       <c r="Y22" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z22" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="23" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>22</v>
       </c>
@@ -2336,33 +2412,33 @@
       <c r="C23" t="s">
         <v>67</v>
       </c>
-      <c r="D23" s="1">
+      <c r="D23" t="s">
+        <v>139</v>
+      </c>
+      <c r="E23" s="1">
         <v>21611</v>
       </c>
-      <c r="E23" s="1">
+      <c r="F23" s="1">
         <v>45667</v>
       </c>
-      <c r="F23">
+      <c r="G23">
         <f>INT((Recueil[[#This Row],[Date_de_recueil]]-Recueil[[#This Row],[DDN]])/365)</f>
         <v>65</v>
       </c>
-      <c r="G23" t="s">
+      <c r="H23" t="s">
         <v>16</v>
       </c>
-      <c r="H23" t="s">
+      <c r="I23" t="s">
         <v>61</v>
       </c>
-      <c r="I23" t="s">
-        <v>7</v>
-      </c>
       <c r="J23" t="s">
         <v>7</v>
       </c>
-      <c r="M23" t="s">
+      <c r="K23" t="s">
         <v>7</v>
       </c>
       <c r="N23" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O23" t="s">
         <v>8</v>
@@ -2376,7 +2452,7 @@
       <c r="R23" t="s">
         <v>8</v>
       </c>
-      <c r="T23" t="s">
+      <c r="S23" t="s">
         <v>8</v>
       </c>
       <c r="U23" t="s">
@@ -2391,8 +2467,11 @@
       <c r="X23" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="24" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="Y23" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>23</v>
       </c>
@@ -2402,29 +2481,29 @@
       <c r="C24" t="s">
         <v>69</v>
       </c>
-      <c r="D24" s="1">
+      <c r="D24" t="s">
+        <v>139</v>
+      </c>
+      <c r="E24" s="1">
         <v>32315</v>
       </c>
-      <c r="E24" s="1">
+      <c r="F24" s="1">
         <v>45650</v>
       </c>
-      <c r="F24">
+      <c r="G24">
         <f>INT((Recueil[[#This Row],[Date_de_recueil]]-Recueil[[#This Row],[DDN]])/365)</f>
         <v>36</v>
       </c>
-      <c r="G24" t="s">
+      <c r="H24" t="s">
         <v>17</v>
       </c>
-      <c r="H24" t="s">
+      <c r="I24" t="s">
         <v>62</v>
       </c>
-      <c r="I24" t="s">
-        <v>8</v>
-      </c>
       <c r="J24" t="s">
         <v>8</v>
       </c>
-      <c r="M24" t="s">
+      <c r="K24" t="s">
         <v>8</v>
       </c>
       <c r="N24" t="s">
@@ -2442,11 +2521,11 @@
       <c r="R24" t="s">
         <v>8</v>
       </c>
-      <c r="T24" t="s">
-        <v>7</v>
+      <c r="S24" t="s">
+        <v>8</v>
       </c>
       <c r="U24" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V24" t="s">
         <v>8</v>
@@ -2457,8 +2536,11 @@
       <c r="X24" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="25" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="Y24" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>24</v>
       </c>
@@ -2468,29 +2550,29 @@
       <c r="C25" t="s">
         <v>71</v>
       </c>
-      <c r="D25" s="1">
+      <c r="D25" t="s">
+        <v>139</v>
+      </c>
+      <c r="E25" s="1">
         <v>35057</v>
       </c>
-      <c r="E25" s="1">
+      <c r="F25" s="1">
         <v>45650</v>
       </c>
-      <c r="F25">
+      <c r="G25">
         <f>INT((Recueil[[#This Row],[Date_de_recueil]]-Recueil[[#This Row],[DDN]])/365)</f>
         <v>29</v>
       </c>
-      <c r="G25" t="s">
+      <c r="H25" t="s">
         <v>17</v>
       </c>
-      <c r="H25" t="s">
+      <c r="I25" t="s">
         <v>65</v>
       </c>
-      <c r="I25" t="s">
-        <v>8</v>
-      </c>
       <c r="J25" t="s">
         <v>8</v>
       </c>
-      <c r="M25" t="s">
+      <c r="K25" t="s">
         <v>8</v>
       </c>
       <c r="N25" t="s">
@@ -2508,7 +2590,7 @@
       <c r="R25" t="s">
         <v>8</v>
       </c>
-      <c r="T25" t="s">
+      <c r="S25" t="s">
         <v>8</v>
       </c>
       <c r="U25" t="s">
@@ -2523,8 +2605,11 @@
       <c r="X25" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="26" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="Y25" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>25</v>
       </c>
@@ -2534,29 +2619,29 @@
       <c r="C26" t="s">
         <v>73</v>
       </c>
-      <c r="D26" s="1">
+      <c r="D26" t="s">
+        <v>138</v>
+      </c>
+      <c r="E26" s="1">
         <v>29029</v>
       </c>
-      <c r="E26" s="1">
+      <c r="F26" s="1">
         <v>45712</v>
       </c>
-      <c r="F26">
+      <c r="G26">
         <f>INT((Recueil[[#This Row],[Date_de_recueil]]-Recueil[[#This Row],[DDN]])/365)</f>
         <v>45</v>
       </c>
-      <c r="G26" t="s">
+      <c r="H26" t="s">
         <v>16</v>
       </c>
-      <c r="H26" t="s">
+      <c r="I26" t="s">
         <v>63</v>
       </c>
-      <c r="I26" t="s">
-        <v>7</v>
-      </c>
       <c r="J26" t="s">
         <v>7</v>
       </c>
-      <c r="M26" t="s">
+      <c r="K26" t="s">
         <v>7</v>
       </c>
       <c r="N26" t="s">
@@ -2566,16 +2651,16 @@
         <v>7</v>
       </c>
       <c r="P26" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q26" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R26" t="s">
-        <v>8</v>
-      </c>
-      <c r="T26" t="s">
-        <v>7</v>
+        <v>7</v>
+      </c>
+      <c r="S26" t="s">
+        <v>8</v>
       </c>
       <c r="U26" t="s">
         <v>7</v>
@@ -2587,10 +2672,13 @@
         <v>7</v>
       </c>
       <c r="X26" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="27" spans="1:37" x14ac:dyDescent="0.2">
+        <v>7</v>
+      </c>
+      <c r="Y26" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>26</v>
       </c>
@@ -2600,34 +2688,34 @@
       <c r="C27" t="s">
         <v>75</v>
       </c>
-      <c r="D27" s="1">
+      <c r="D27" t="s">
+        <v>138</v>
+      </c>
+      <c r="E27" s="1">
         <v>20742</v>
       </c>
-      <c r="E27" s="1">
+      <c r="F27" s="1">
         <v>45693</v>
       </c>
-      <c r="F27">
+      <c r="G27">
         <f>INT((Recueil[[#This Row],[Date_de_recueil]]-Recueil[[#This Row],[DDN]])/365)</f>
         <v>68</v>
       </c>
-      <c r="G27" t="s">
+      <c r="H27" t="s">
         <v>17</v>
       </c>
-      <c r="H27" t="s">
+      <c r="I27" t="s">
         <v>64</v>
       </c>
-      <c r="I27" t="s">
-        <v>7</v>
-      </c>
       <c r="J27" t="s">
+        <v>7</v>
+      </c>
+      <c r="K27" t="s">
         <v>3</v>
       </c>
-      <c r="M27" t="s">
+      <c r="N27" t="s">
         <v>3</v>
       </c>
-      <c r="N27" t="s">
-        <v>7</v>
-      </c>
       <c r="O27" t="s">
         <v>7</v>
       </c>
@@ -2638,11 +2726,11 @@
         <v>7</v>
       </c>
       <c r="R27" t="s">
+        <v>7</v>
+      </c>
+      <c r="S27" t="s">
         <v>13</v>
       </c>
-      <c r="T27" t="s">
-        <v>7</v>
-      </c>
       <c r="U27" t="s">
         <v>7</v>
       </c>
@@ -2653,10 +2741,13 @@
         <v>7</v>
       </c>
       <c r="X27" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y27" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>27</v>
       </c>
@@ -2666,29 +2757,29 @@
       <c r="C28" t="s">
         <v>77</v>
       </c>
-      <c r="D28" s="1">
+      <c r="D28" t="s">
+        <v>138</v>
+      </c>
+      <c r="E28" s="1">
         <v>19470</v>
       </c>
-      <c r="E28" s="1">
+      <c r="F28" s="1">
         <v>45719</v>
       </c>
-      <c r="F28">
+      <c r="G28">
         <f>INT((Recueil[[#This Row],[Date_de_recueil]]-Recueil[[#This Row],[DDN]])/365)</f>
         <v>71</v>
       </c>
-      <c r="G28" t="s">
+      <c r="H28" t="s">
         <v>17</v>
       </c>
-      <c r="H28" t="s">
+      <c r="I28" t="s">
         <v>63</v>
       </c>
-      <c r="I28" t="s">
-        <v>7</v>
-      </c>
       <c r="J28" t="s">
         <v>7</v>
       </c>
-      <c r="M28" t="s">
+      <c r="K28" t="s">
         <v>7</v>
       </c>
       <c r="N28" t="s">
@@ -2698,7 +2789,7 @@
         <v>7</v>
       </c>
       <c r="P28" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q28" t="s">
         <v>8</v>
@@ -2706,14 +2797,14 @@
       <c r="R28" t="s">
         <v>8</v>
       </c>
-      <c r="T28" t="s">
-        <v>7</v>
+      <c r="S28" t="s">
+        <v>8</v>
       </c>
       <c r="U28" t="s">
         <v>7</v>
       </c>
       <c r="V28" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W28" t="s">
         <v>8</v>
@@ -2721,8 +2812,11 @@
       <c r="X28" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="29" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="Y28" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>28</v>
       </c>
@@ -2732,29 +2826,29 @@
       <c r="C29" t="s">
         <v>77</v>
       </c>
-      <c r="D29" s="1">
+      <c r="D29" t="s">
+        <v>138</v>
+      </c>
+      <c r="E29" s="1">
         <v>19470</v>
       </c>
-      <c r="E29" s="1">
+      <c r="F29" s="1">
         <v>45719</v>
       </c>
-      <c r="F29">
+      <c r="G29">
         <f>INT((Recueil[[#This Row],[Date_de_recueil]]-Recueil[[#This Row],[DDN]])/365)</f>
         <v>71</v>
       </c>
-      <c r="G29" t="s">
+      <c r="H29" t="s">
         <v>16</v>
       </c>
-      <c r="H29" t="s">
+      <c r="I29" t="s">
         <v>63</v>
       </c>
-      <c r="I29" t="s">
-        <v>7</v>
-      </c>
       <c r="J29" t="s">
         <v>7</v>
       </c>
-      <c r="M29" t="s">
+      <c r="K29" t="s">
         <v>7</v>
       </c>
       <c r="N29" t="s">
@@ -2767,13 +2861,13 @@
         <v>7</v>
       </c>
       <c r="Q29" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R29" t="s">
         <v>8</v>
       </c>
-      <c r="T29" t="s">
-        <v>7</v>
+      <c r="S29" t="s">
+        <v>8</v>
       </c>
       <c r="U29" t="s">
         <v>7</v>
@@ -2782,13 +2876,16 @@
         <v>7</v>
       </c>
       <c r="W29" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X29" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="Y29" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>29</v>
       </c>
@@ -2798,33 +2895,33 @@
       <c r="C30" t="s">
         <v>79</v>
       </c>
-      <c r="D30" s="1">
+      <c r="D30" t="s">
+        <v>139</v>
+      </c>
+      <c r="E30" s="1">
         <v>33137</v>
       </c>
-      <c r="E30" s="1">
+      <c r="F30" s="1">
         <v>45719</v>
       </c>
-      <c r="F30">
+      <c r="G30">
         <v>34</v>
       </c>
-      <c r="G30" t="s">
+      <c r="H30" t="s">
         <v>17</v>
       </c>
-      <c r="H30" t="s">
+      <c r="I30" t="s">
         <v>65</v>
       </c>
-      <c r="I30" t="s">
-        <v>7</v>
-      </c>
       <c r="J30" t="s">
         <v>7</v>
       </c>
       <c r="K30" t="s">
+        <v>7</v>
+      </c>
+      <c r="L30" t="s">
         <v>1</v>
       </c>
-      <c r="M30" t="s">
-        <v>7</v>
-      </c>
       <c r="N30" t="s">
         <v>7</v>
       </c>
@@ -2835,13 +2932,13 @@
         <v>7</v>
       </c>
       <c r="Q30" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R30" t="s">
         <v>8</v>
       </c>
-      <c r="T30" t="s">
-        <v>7</v>
+      <c r="S30" t="s">
+        <v>8</v>
       </c>
       <c r="U30" t="s">
         <v>7</v>
@@ -2850,13 +2947,16 @@
         <v>7</v>
       </c>
       <c r="W30" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X30" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="31" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="Y30" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>30</v>
       </c>
@@ -2866,34 +2966,34 @@
       <c r="C31" t="s">
         <v>79</v>
       </c>
-      <c r="D31" s="1">
+      <c r="D31" t="s">
+        <v>139</v>
+      </c>
+      <c r="E31" s="1">
         <v>33137</v>
       </c>
-      <c r="E31" s="1">
+      <c r="F31" s="1">
         <v>45719</v>
       </c>
-      <c r="F31">
+      <c r="G31">
         <f>INT((Recueil[[#This Row],[Date_de_recueil]]-Recueil[[#This Row],[DDN]])/365)</f>
         <v>34</v>
       </c>
-      <c r="G31" t="s">
+      <c r="H31" t="s">
         <v>16</v>
       </c>
-      <c r="H31" t="s">
+      <c r="I31" t="s">
         <v>65</v>
       </c>
-      <c r="I31" t="s">
-        <v>7</v>
-      </c>
       <c r="J31" t="s">
         <v>7</v>
       </c>
       <c r="K31" t="s">
+        <v>7</v>
+      </c>
+      <c r="L31" t="s">
         <v>1</v>
       </c>
-      <c r="M31" t="s">
-        <v>7</v>
-      </c>
       <c r="N31" t="s">
         <v>7</v>
       </c>
@@ -2904,13 +3004,13 @@
         <v>7</v>
       </c>
       <c r="Q31" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R31" t="s">
         <v>8</v>
       </c>
-      <c r="T31" t="s">
-        <v>7</v>
+      <c r="S31" t="s">
+        <v>8</v>
       </c>
       <c r="U31" t="s">
         <v>7</v>
@@ -2919,14 +3019,17 @@
         <v>7</v>
       </c>
       <c r="W31" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X31" t="s">
         <v>8</v>
       </c>
-      <c r="AK31" s="3"/>
-    </row>
-    <row r="32" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="Y31" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL31" s="3"/>
+    </row>
+    <row r="32" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>31</v>
       </c>
@@ -2936,39 +3039,39 @@
       <c r="C32" t="s">
         <v>82</v>
       </c>
-      <c r="D32" s="1">
+      <c r="D32" t="s">
+        <v>139</v>
+      </c>
+      <c r="E32" s="1">
         <v>28262</v>
       </c>
-      <c r="E32" s="1">
+      <c r="F32" s="1">
         <v>45712</v>
       </c>
-      <c r="F32">
+      <c r="G32">
         <f>INT((Recueil[[#This Row],[Date_de_recueil]]-Recueil[[#This Row],[DDN]])/365)</f>
         <v>47</v>
       </c>
-      <c r="G32" t="s">
+      <c r="H32" t="s">
         <v>16</v>
       </c>
-      <c r="H32" t="s">
+      <c r="I32" t="s">
         <v>65</v>
       </c>
-      <c r="I32" t="s">
-        <v>7</v>
-      </c>
       <c r="J32" t="s">
         <v>7</v>
       </c>
       <c r="K32" t="s">
+        <v>7</v>
+      </c>
+      <c r="L32" t="s">
         <v>1</v>
       </c>
-      <c r="M32" t="s">
-        <v>7</v>
-      </c>
       <c r="N32" t="s">
         <v>7</v>
       </c>
       <c r="O32" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P32" t="s">
         <v>8</v>
@@ -2979,14 +3082,14 @@
       <c r="R32" t="s">
         <v>8</v>
       </c>
-      <c r="T32" t="s">
-        <v>7</v>
+      <c r="S32" t="s">
+        <v>8</v>
       </c>
       <c r="U32" t="s">
         <v>7</v>
       </c>
       <c r="V32" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W32" t="s">
         <v>8</v>
@@ -2994,8 +3097,11 @@
       <c r="X32" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="33" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="Y32" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>32</v>
       </c>
@@ -3005,36 +3111,36 @@
       <c r="C33" t="s">
         <v>84</v>
       </c>
-      <c r="D33" s="1">
+      <c r="D33" t="s">
+        <v>138</v>
+      </c>
+      <c r="E33" s="1">
         <v>34794</v>
       </c>
-      <c r="E33" s="1">
+      <c r="F33" s="1">
         <v>45691</v>
       </c>
-      <c r="F33">
+      <c r="G33">
         <v>29</v>
       </c>
-      <c r="G33" t="s">
+      <c r="H33" t="s">
         <v>17</v>
       </c>
-      <c r="H33" t="s">
+      <c r="I33" t="s">
         <v>65</v>
       </c>
-      <c r="I33" t="s">
-        <v>7</v>
-      </c>
       <c r="J33" t="s">
+        <v>7</v>
+      </c>
+      <c r="K33" t="s">
         <v>3</v>
       </c>
-      <c r="K33" t="s">
+      <c r="L33" t="s">
         <v>1</v>
       </c>
-      <c r="M33" t="s">
+      <c r="N33" t="s">
         <v>3</v>
       </c>
-      <c r="N33" t="s">
-        <v>7</v>
-      </c>
       <c r="O33" t="s">
         <v>7</v>
       </c>
@@ -3045,10 +3151,10 @@
         <v>7</v>
       </c>
       <c r="R33" t="s">
-        <v>8</v>
-      </c>
-      <c r="T33" t="s">
-        <v>7</v>
+        <v>7</v>
+      </c>
+      <c r="S33" t="s">
+        <v>8</v>
       </c>
       <c r="U33" t="s">
         <v>7</v>
@@ -3057,14 +3163,17 @@
         <v>7</v>
       </c>
       <c r="W33" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X33" t="s">
         <v>8</v>
       </c>
-      <c r="AG33" s="3"/>
-    </row>
-    <row r="34" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="Y33" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH33" s="3"/>
+    </row>
+    <row r="34" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>33</v>
       </c>
@@ -3074,33 +3183,33 @@
       <c r="C34" t="s">
         <v>86</v>
       </c>
-      <c r="D34" s="1">
+      <c r="D34" t="s">
+        <v>139</v>
+      </c>
+      <c r="E34" s="1">
         <v>30397</v>
       </c>
-      <c r="E34" s="1">
+      <c r="F34" s="1">
         <v>45691</v>
       </c>
-      <c r="F34">
+      <c r="G34">
         <f>INT((Recueil[[#This Row],[Date_de_recueil]]-Recueil[[#This Row],[DDN]])/365)</f>
         <v>41</v>
       </c>
-      <c r="G34" t="s">
+      <c r="H34" t="s">
         <v>17</v>
       </c>
-      <c r="H34" t="s">
+      <c r="I34" t="s">
         <v>63</v>
       </c>
-      <c r="I34" t="s">
-        <v>7</v>
-      </c>
       <c r="J34" t="s">
-        <v>8</v>
-      </c>
-      <c r="M34" t="s">
+        <v>7</v>
+      </c>
+      <c r="K34" t="s">
         <v>8</v>
       </c>
       <c r="N34" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O34" t="s">
         <v>7</v>
@@ -3112,10 +3221,10 @@
         <v>7</v>
       </c>
       <c r="R34" t="s">
-        <v>8</v>
-      </c>
-      <c r="T34" t="s">
-        <v>7</v>
+        <v>7</v>
+      </c>
+      <c r="S34" t="s">
+        <v>8</v>
       </c>
       <c r="U34" t="s">
         <v>7</v>
@@ -3130,10 +3239,13 @@
         <v>7</v>
       </c>
       <c r="Y34" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z34" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="35" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>34</v>
       </c>
@@ -3143,33 +3255,33 @@
       <c r="C35" t="s">
         <v>86</v>
       </c>
-      <c r="D35" s="1">
+      <c r="D35" t="s">
+        <v>139</v>
+      </c>
+      <c r="E35" s="1">
         <v>30397</v>
       </c>
-      <c r="E35" s="1">
+      <c r="F35" s="1">
         <v>45691</v>
       </c>
-      <c r="F35">
+      <c r="G35">
         <f>INT((Recueil[[#This Row],[Date_de_recueil]]-Recueil[[#This Row],[DDN]])/365)</f>
         <v>41</v>
       </c>
-      <c r="G35" t="s">
+      <c r="H35" t="s">
         <v>16</v>
       </c>
-      <c r="H35" t="s">
+      <c r="I35" t="s">
         <v>63</v>
       </c>
-      <c r="I35" t="s">
-        <v>7</v>
-      </c>
       <c r="J35" t="s">
-        <v>8</v>
-      </c>
-      <c r="M35" t="s">
+        <v>7</v>
+      </c>
+      <c r="K35" t="s">
         <v>8</v>
       </c>
       <c r="N35" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O35" t="s">
         <v>7</v>
@@ -3181,10 +3293,10 @@
         <v>7</v>
       </c>
       <c r="R35" t="s">
-        <v>8</v>
-      </c>
-      <c r="T35" t="s">
-        <v>7</v>
+        <v>7</v>
+      </c>
+      <c r="S35" t="s">
+        <v>8</v>
       </c>
       <c r="U35" t="s">
         <v>7</v>
@@ -3199,10 +3311,13 @@
         <v>7</v>
       </c>
       <c r="Y35" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z35" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>35</v>
       </c>
@@ -3212,65 +3327,68 @@
       <c r="C36" t="s">
         <v>88</v>
       </c>
-      <c r="D36" s="1">
+      <c r="D36" t="s">
+        <v>138</v>
+      </c>
+      <c r="E36" s="1">
         <v>27302</v>
       </c>
-      <c r="E36" s="4">
+      <c r="F36" s="4">
         <v>45749</v>
       </c>
-      <c r="F36">
+      <c r="G36">
         <v>50</v>
       </c>
-      <c r="G36" t="s">
+      <c r="H36" t="s">
         <v>17</v>
       </c>
-      <c r="H36" t="s">
+      <c r="I36" t="s">
         <v>65</v>
       </c>
-      <c r="I36" t="s">
-        <v>7</v>
-      </c>
       <c r="J36" t="s">
         <v>7</v>
       </c>
       <c r="K36" t="s">
+        <v>7</v>
+      </c>
+      <c r="L36" t="s">
         <v>1</v>
       </c>
-      <c r="M36" t="s">
-        <v>7</v>
-      </c>
       <c r="N36" t="s">
         <v>7</v>
       </c>
       <c r="O36" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P36" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q36" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R36" t="s">
         <v>8</v>
       </c>
-      <c r="T36" t="s">
-        <v>7</v>
+      <c r="S36" t="s">
+        <v>8</v>
       </c>
       <c r="U36" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V36" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W36" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X36" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="37" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="Y36" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>36</v>
       </c>
@@ -3280,63 +3398,66 @@
       <c r="C37" t="s">
         <v>28</v>
       </c>
-      <c r="D37" s="1">
+      <c r="D37" t="s">
+        <v>138</v>
+      </c>
+      <c r="E37" s="1">
         <v>26462</v>
       </c>
-      <c r="E37" s="1">
+      <c r="F37" s="1">
         <v>45729</v>
       </c>
-      <c r="F37">
+      <c r="G37">
         <f>INT((Recueil[[#This Row],[Date_de_recueil]]-Recueil[[#This Row],[DDN]])/365)</f>
         <v>52</v>
       </c>
-      <c r="G37" t="s">
+      <c r="H37" t="s">
         <v>17</v>
       </c>
-      <c r="H37" t="s">
+      <c r="I37" t="s">
         <v>63</v>
       </c>
-      <c r="I37" t="s">
-        <v>7</v>
-      </c>
       <c r="J37" t="s">
         <v>7</v>
       </c>
-      <c r="M37" t="s">
+      <c r="K37" t="s">
         <v>7</v>
       </c>
       <c r="N37" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O37" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P37" t="s">
         <v>7</v>
       </c>
       <c r="Q37" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R37" t="s">
         <v>8</v>
       </c>
-      <c r="T37" t="s">
+      <c r="S37" t="s">
         <v>8</v>
       </c>
       <c r="U37" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V37" t="s">
         <v>7</v>
       </c>
       <c r="W37" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X37" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="38" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="Y37" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>37</v>
       </c>
@@ -3346,33 +3467,33 @@
       <c r="C38" t="s">
         <v>91</v>
       </c>
-      <c r="D38" s="1">
+      <c r="D38" t="s">
+        <v>138</v>
+      </c>
+      <c r="E38" s="1">
         <v>33438</v>
       </c>
-      <c r="E38" s="1">
+      <c r="F38" s="1">
         <v>45740</v>
       </c>
-      <c r="F38">
+      <c r="G38">
         <f>INT((Recueil[[#This Row],[Date_de_recueil]]-Recueil[[#This Row],[DDN]])/365)</f>
         <v>33</v>
       </c>
-      <c r="G38" t="s">
+      <c r="H38" t="s">
         <v>16</v>
       </c>
-      <c r="H38" t="s">
+      <c r="I38" t="s">
         <v>63</v>
       </c>
-      <c r="I38" t="s">
-        <v>7</v>
-      </c>
       <c r="J38" t="s">
-        <v>8</v>
-      </c>
-      <c r="M38" t="s">
+        <v>7</v>
+      </c>
+      <c r="K38" t="s">
         <v>8</v>
       </c>
       <c r="N38" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O38" t="s">
         <v>7</v>
@@ -3381,13 +3502,13 @@
         <v>7</v>
       </c>
       <c r="Q38" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R38" t="s">
         <v>8</v>
       </c>
-      <c r="T38" t="s">
-        <v>7</v>
+      <c r="S38" t="s">
+        <v>8</v>
       </c>
       <c r="U38" t="s">
         <v>7</v>
@@ -3399,10 +3520,13 @@
         <v>7</v>
       </c>
       <c r="X38" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="39" spans="1:33" x14ac:dyDescent="0.2">
+        <v>7</v>
+      </c>
+      <c r="Y38" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>38</v>
       </c>
@@ -3412,29 +3536,29 @@
       <c r="C39" t="s">
         <v>93</v>
       </c>
-      <c r="D39" s="1">
+      <c r="D39" t="s">
+        <v>138</v>
+      </c>
+      <c r="E39" s="1">
         <v>25203</v>
       </c>
-      <c r="E39" s="1">
+      <c r="F39" s="1">
         <v>45740</v>
       </c>
-      <c r="F39">
+      <c r="G39">
         <f>INT((Recueil[[#This Row],[Date_de_recueil]]-Recueil[[#This Row],[DDN]])/365)</f>
         <v>56</v>
       </c>
-      <c r="G39" t="s">
+      <c r="H39" t="s">
         <v>16</v>
       </c>
-      <c r="H39" t="s">
+      <c r="I39" t="s">
         <v>63</v>
       </c>
-      <c r="I39" t="s">
-        <v>7</v>
-      </c>
       <c r="J39" t="s">
         <v>7</v>
       </c>
-      <c r="M39" t="s">
+      <c r="K39" t="s">
         <v>7</v>
       </c>
       <c r="N39" t="s">
@@ -3447,13 +3571,13 @@
         <v>7</v>
       </c>
       <c r="Q39" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R39" t="s">
         <v>8</v>
       </c>
-      <c r="T39" t="s">
-        <v>7</v>
+      <c r="S39" t="s">
+        <v>8</v>
       </c>
       <c r="U39" t="s">
         <v>7</v>
@@ -3462,13 +3586,16 @@
         <v>7</v>
       </c>
       <c r="W39" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X39" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="40" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="Y39" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="40" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>39</v>
       </c>
@@ -3478,34 +3605,34 @@
       <c r="C40" t="s">
         <v>95</v>
       </c>
-      <c r="D40" s="1">
+      <c r="D40" t="s">
+        <v>139</v>
+      </c>
+      <c r="E40" s="1">
         <v>27375</v>
       </c>
-      <c r="E40" s="1">
+      <c r="F40" s="1">
         <v>45740</v>
       </c>
-      <c r="F40">
+      <c r="G40">
         <f>INT((Recueil[[#This Row],[Date_de_recueil]]-Recueil[[#This Row],[DDN]])/365)</f>
         <v>50</v>
       </c>
-      <c r="G40" t="s">
+      <c r="H40" t="s">
         <v>17</v>
       </c>
-      <c r="H40" t="s">
+      <c r="I40" t="s">
         <v>63</v>
       </c>
-      <c r="I40" t="s">
-        <v>7</v>
-      </c>
       <c r="J40" t="s">
         <v>7</v>
       </c>
       <c r="K40" t="s">
+        <v>7</v>
+      </c>
+      <c r="L40" t="s">
         <v>0</v>
       </c>
-      <c r="L40" t="s">
-        <v>7</v>
-      </c>
       <c r="M40" t="s">
         <v>7</v>
       </c>
@@ -3519,28 +3646,31 @@
         <v>7</v>
       </c>
       <c r="Q40" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R40" t="s">
         <v>8</v>
       </c>
-      <c r="T40" t="s">
-        <v>7</v>
+      <c r="S40" t="s">
+        <v>8</v>
       </c>
       <c r="U40" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V40" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W40" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X40" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="41" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="Y40" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="41" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>40</v>
       </c>
@@ -3550,34 +3680,34 @@
       <c r="C41" t="s">
         <v>95</v>
       </c>
-      <c r="D41" s="1">
+      <c r="D41" t="s">
+        <v>139</v>
+      </c>
+      <c r="E41" s="1">
         <v>27375</v>
       </c>
-      <c r="E41" s="1">
+      <c r="F41" s="1">
         <v>45740</v>
       </c>
-      <c r="F41">
+      <c r="G41">
         <f>INT((Recueil[[#This Row],[Date_de_recueil]]-Recueil[[#This Row],[DDN]])/365)</f>
         <v>50</v>
       </c>
-      <c r="G41" t="s">
+      <c r="H41" t="s">
         <v>16</v>
       </c>
-      <c r="H41" t="s">
+      <c r="I41" t="s">
         <v>63</v>
       </c>
-      <c r="I41" t="s">
-        <v>7</v>
-      </c>
       <c r="J41" t="s">
         <v>7</v>
       </c>
       <c r="K41" t="s">
+        <v>7</v>
+      </c>
+      <c r="L41" t="s">
         <v>0</v>
       </c>
-      <c r="L41" t="s">
-        <v>7</v>
-      </c>
       <c r="M41" t="s">
         <v>7</v>
       </c>
@@ -3585,23 +3715,23 @@
         <v>7</v>
       </c>
       <c r="O41" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P41" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q41" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R41" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S41" t="s">
+        <v>7</v>
+      </c>
+      <c r="T41" t="s">
         <v>25</v>
       </c>
-      <c r="T41" t="s">
-        <v>7</v>
-      </c>
       <c r="U41" t="s">
         <v>7</v>
       </c>
@@ -3609,13 +3739,16 @@
         <v>7</v>
       </c>
       <c r="W41" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X41" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="42" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="Y41" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>41</v>
       </c>
@@ -3625,34 +3758,34 @@
       <c r="C42" t="s">
         <v>97</v>
       </c>
-      <c r="D42" s="1">
+      <c r="D42" t="s">
+        <v>138</v>
+      </c>
+      <c r="E42" s="1">
         <v>26759</v>
       </c>
-      <c r="E42" s="1">
+      <c r="F42" s="1">
         <v>45735</v>
       </c>
-      <c r="F42">
+      <c r="G42">
         <f>INT((Recueil[[#This Row],[Date_de_recueil]]-Recueil[[#This Row],[DDN]])/365)</f>
         <v>51</v>
       </c>
-      <c r="G42" t="s">
+      <c r="H42" t="s">
         <v>17</v>
       </c>
-      <c r="H42" t="s">
+      <c r="I42" t="s">
         <v>63</v>
       </c>
-      <c r="I42" t="s">
-        <v>7</v>
-      </c>
       <c r="J42" t="s">
         <v>7</v>
       </c>
       <c r="K42" t="s">
+        <v>7</v>
+      </c>
+      <c r="L42" t="s">
         <v>0</v>
       </c>
-      <c r="L42" t="s">
-        <v>7</v>
-      </c>
       <c r="M42" t="s">
         <v>7</v>
       </c>
@@ -3666,17 +3799,17 @@
         <v>7</v>
       </c>
       <c r="Q42" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R42" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S42" t="s">
+        <v>7</v>
+      </c>
+      <c r="T42" t="s">
         <v>25</v>
       </c>
-      <c r="T42" t="s">
-        <v>7</v>
-      </c>
       <c r="U42" t="s">
         <v>7</v>
       </c>
@@ -3684,16 +3817,19 @@
         <v>7</v>
       </c>
       <c r="W42" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X42" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y42" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z42" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="43" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>42</v>
       </c>
@@ -3703,34 +3839,34 @@
       <c r="C43" t="s">
         <v>23</v>
       </c>
-      <c r="D43" s="1">
+      <c r="D43" t="s">
+        <v>138</v>
+      </c>
+      <c r="E43" s="1">
         <v>27134</v>
       </c>
-      <c r="E43" s="1">
+      <c r="F43" s="1">
         <v>45744</v>
       </c>
-      <c r="F43">
+      <c r="G43">
         <f>INT((Recueil[[#This Row],[Date_de_recueil]]-Recueil[[#This Row],[DDN]])/365)</f>
         <v>50</v>
       </c>
-      <c r="G43" t="s">
+      <c r="H43" t="s">
         <v>16</v>
       </c>
-      <c r="H43" t="s">
+      <c r="I43" t="s">
         <v>65</v>
       </c>
-      <c r="I43" t="s">
-        <v>7</v>
-      </c>
       <c r="J43" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K43" t="s">
+        <v>8</v>
+      </c>
+      <c r="L43" t="s">
         <v>1</v>
       </c>
-      <c r="M43" t="s">
-        <v>8</v>
-      </c>
       <c r="N43" t="s">
         <v>8</v>
       </c>
@@ -3746,7 +3882,7 @@
       <c r="R43" t="s">
         <v>8</v>
       </c>
-      <c r="T43" t="s">
+      <c r="S43" t="s">
         <v>8</v>
       </c>
       <c r="U43" t="s">
@@ -3761,8 +3897,11 @@
       <c r="X43" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="44" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="Y43" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>43</v>
       </c>
@@ -3772,33 +3911,33 @@
       <c r="C44" t="s">
         <v>100</v>
       </c>
-      <c r="D44" s="1">
+      <c r="D44" t="s">
+        <v>139</v>
+      </c>
+      <c r="E44" s="1">
         <v>24986</v>
       </c>
-      <c r="E44" s="1">
+      <c r="F44" s="1">
         <v>45754</v>
       </c>
-      <c r="F44">
+      <c r="G44">
         <f>INT((Recueil[[#This Row],[Date_de_recueil]]-Recueil[[#This Row],[DDN]])/365)</f>
         <v>56</v>
       </c>
-      <c r="G44" t="s">
+      <c r="H44" t="s">
         <v>16</v>
       </c>
-      <c r="H44" t="s">
+      <c r="I44" t="s">
         <v>65</v>
       </c>
-      <c r="I44" t="s">
-        <v>7</v>
-      </c>
       <c r="J44" t="s">
         <v>7</v>
       </c>
-      <c r="M44" t="s">
+      <c r="K44" t="s">
         <v>7</v>
       </c>
       <c r="N44" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O44" t="s">
         <v>8</v>
@@ -3812,8 +3951,8 @@
       <c r="R44" t="s">
         <v>8</v>
       </c>
-      <c r="T44" t="s">
-        <v>13</v>
+      <c r="S44" t="s">
+        <v>8</v>
       </c>
       <c r="U44" t="s">
         <v>13</v>
@@ -3827,8 +3966,11 @@
       <c r="X44" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="45" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="Y44" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="45" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>44</v>
       </c>
@@ -3838,36 +3980,36 @@
       <c r="C45" t="s">
         <v>102</v>
       </c>
-      <c r="D45" s="1">
+      <c r="D45" t="s">
+        <v>138</v>
+      </c>
+      <c r="E45" s="1">
         <v>17869</v>
       </c>
-      <c r="E45" s="1">
+      <c r="F45" s="1">
         <v>45762</v>
       </c>
-      <c r="F45">
+      <c r="G45">
         <f>INT((Recueil[[#This Row],[Date_de_recueil]]-Recueil[[#This Row],[DDN]])/365)</f>
         <v>76</v>
       </c>
-      <c r="G45" t="s">
+      <c r="H45" t="s">
         <v>16</v>
       </c>
-      <c r="H45" t="s">
+      <c r="I45" t="s">
         <v>63</v>
       </c>
-      <c r="I45" t="s">
-        <v>7</v>
-      </c>
       <c r="J45" t="s">
         <v>7</v>
       </c>
-      <c r="M45" t="s">
+      <c r="K45" t="s">
         <v>7</v>
       </c>
       <c r="N45" t="s">
         <v>7</v>
       </c>
       <c r="O45" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P45" t="s">
         <v>8</v>
@@ -3878,8 +4020,8 @@
       <c r="R45" t="s">
         <v>8</v>
       </c>
-      <c r="T45" t="s">
-        <v>13</v>
+      <c r="S45" t="s">
+        <v>8</v>
       </c>
       <c r="U45" t="s">
         <v>13</v>
@@ -3893,8 +4035,11 @@
       <c r="X45" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="46" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="Y45" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="46" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>45</v>
       </c>
@@ -3904,23 +4049,23 @@
       <c r="C46" t="s">
         <v>104</v>
       </c>
-      <c r="D46" s="1">
+      <c r="D46" t="s">
+        <v>138</v>
+      </c>
+      <c r="E46" s="1">
         <v>30264</v>
       </c>
-      <c r="E46" s="1">
+      <c r="F46" s="1">
         <v>45775</v>
       </c>
-      <c r="F46">
+      <c r="G46">
         <f>INT((Recueil[[#This Row],[Date_de_recueil]]-Recueil[[#This Row],[DDN]])/365)</f>
         <v>42</v>
       </c>
-      <c r="I46" t="s">
-        <v>7</v>
-      </c>
       <c r="J46" t="s">
         <v>7</v>
       </c>
-      <c r="M46" t="s">
+      <c r="K46" t="s">
         <v>7</v>
       </c>
       <c r="N46" t="s">
@@ -3936,16 +4081,16 @@
         <v>7</v>
       </c>
       <c r="R46" t="s">
-        <v>8</v>
-      </c>
-      <c r="T46" t="s">
-        <v>7</v>
+        <v>7</v>
+      </c>
+      <c r="S46" t="s">
+        <v>8</v>
       </c>
       <c r="U46" t="s">
         <v>7</v>
       </c>
       <c r="V46" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W46" t="s">
         <v>8</v>
@@ -3953,8 +4098,11 @@
       <c r="X46" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="47" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="Y46" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>46</v>
       </c>
@@ -3964,23 +4112,23 @@
       <c r="C47" t="s">
         <v>106</v>
       </c>
-      <c r="D47" s="1">
+      <c r="D47" t="s">
+        <v>139</v>
+      </c>
+      <c r="E47" s="1">
         <v>25221</v>
       </c>
-      <c r="E47" s="1">
+      <c r="F47" s="1">
         <v>45796</v>
       </c>
-      <c r="F47">
+      <c r="G47">
         <f>INT((Recueil[[#This Row],[Date_de_recueil]]-Recueil[[#This Row],[DDN]])/365)</f>
         <v>56</v>
       </c>
-      <c r="I47" t="s">
-        <v>7</v>
-      </c>
       <c r="J47" t="s">
         <v>7</v>
       </c>
-      <c r="M47" t="s">
+      <c r="K47" t="s">
         <v>7</v>
       </c>
       <c r="N47" t="s">
@@ -3990,31 +4138,34 @@
         <v>7</v>
       </c>
       <c r="P47" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q47" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R47" t="s">
-        <v>8</v>
-      </c>
-      <c r="T47" t="s">
-        <v>7</v>
+        <v>7</v>
+      </c>
+      <c r="S47" t="s">
+        <v>8</v>
       </c>
       <c r="U47" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V47" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W47" t="s">
         <v>7</v>
       </c>
       <c r="X47" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="48" spans="1:33" x14ac:dyDescent="0.2">
+        <v>7</v>
+      </c>
+      <c r="Y47" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>47</v>
       </c>
@@ -4024,23 +4175,23 @@
       <c r="C48" t="s">
         <v>108</v>
       </c>
-      <c r="D48" s="1">
+      <c r="D48" t="s">
+        <v>138</v>
+      </c>
+      <c r="E48" s="1">
         <v>35938</v>
       </c>
-      <c r="E48" s="1">
+      <c r="F48" s="1">
         <v>45796</v>
       </c>
-      <c r="F48">
+      <c r="G48">
         <f>INT((Recueil[[#This Row],[Date_de_recueil]]-Recueil[[#This Row],[DDN]])/365)</f>
         <v>27</v>
       </c>
-      <c r="I48" t="s">
-        <v>8</v>
-      </c>
       <c r="J48" t="s">
         <v>8</v>
       </c>
-      <c r="M48" t="s">
+      <c r="K48" t="s">
         <v>8</v>
       </c>
       <c r="N48" t="s">
@@ -4058,7 +4209,7 @@
       <c r="R48" t="s">
         <v>8</v>
       </c>
-      <c r="T48" t="s">
+      <c r="S48" t="s">
         <v>8</v>
       </c>
       <c r="U48" t="s">
@@ -4073,8 +4224,11 @@
       <c r="X48" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="49" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Y48" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>48</v>
       </c>
@@ -4084,21 +4238,21 @@
       <c r="C49" t="s">
         <v>110</v>
       </c>
-      <c r="E49" s="1">
+      <c r="D49" t="s">
+        <v>138</v>
+      </c>
+      <c r="F49" s="1">
         <v>45796</v>
       </c>
-      <c r="F49">
+      <c r="G49">
         <f>INT((Recueil[[#This Row],[Date_de_recueil]]-Recueil[[#This Row],[DDN]])/365)</f>
         <v>125</v>
-      </c>
-      <c r="I49" t="s">
-        <v>3</v>
       </c>
       <c r="J49" t="s">
         <v>3</v>
       </c>
-      <c r="M49" t="s">
-        <v>7</v>
+      <c r="K49" t="s">
+        <v>3</v>
       </c>
       <c r="N49" t="s">
         <v>7</v>
@@ -4113,10 +4267,10 @@
         <v>7</v>
       </c>
       <c r="R49" t="s">
-        <v>8</v>
-      </c>
-      <c r="T49" t="s">
-        <v>7</v>
+        <v>7</v>
+      </c>
+      <c r="S49" t="s">
+        <v>8</v>
       </c>
       <c r="U49" t="s">
         <v>7</v>
@@ -4128,10 +4282,13 @@
         <v>7</v>
       </c>
       <c r="X49" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="50" spans="1:25" x14ac:dyDescent="0.2">
+        <v>7</v>
+      </c>
+      <c r="Y49" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>49</v>
       </c>
@@ -4141,26 +4298,26 @@
       <c r="C50" t="s">
         <v>77</v>
       </c>
-      <c r="D50" s="1">
+      <c r="D50" t="s">
+        <v>138</v>
+      </c>
+      <c r="E50" s="1">
         <v>19374</v>
       </c>
-      <c r="E50" s="1">
+      <c r="F50" s="1">
         <v>45784</v>
       </c>
-      <c r="F50">
+      <c r="G50">
         <f>INT((Recueil[[#This Row],[Date_de_recueil]]-Recueil[[#This Row],[DDN]])/365)</f>
         <v>72</v>
       </c>
-      <c r="G50" t="s">
+      <c r="H50" t="s">
         <v>17</v>
       </c>
-      <c r="I50" t="s">
-        <v>8</v>
-      </c>
       <c r="J50" t="s">
         <v>8</v>
       </c>
-      <c r="M50" t="s">
+      <c r="K50" t="s">
         <v>8</v>
       </c>
       <c r="N50" t="s">
@@ -4178,23 +4335,26 @@
       <c r="R50" t="s">
         <v>8</v>
       </c>
-      <c r="T50" t="s">
+      <c r="S50" t="s">
         <v>8</v>
       </c>
       <c r="U50" t="s">
         <v>8</v>
       </c>
       <c r="V50" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W50" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X50" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="51" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Y50" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="51" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>50</v>
       </c>
@@ -4204,26 +4364,26 @@
       <c r="C51" t="s">
         <v>77</v>
       </c>
-      <c r="D51" s="1">
+      <c r="D51" t="s">
+        <v>138</v>
+      </c>
+      <c r="E51" s="1">
         <v>19374</v>
       </c>
-      <c r="E51" s="1">
+      <c r="F51" s="1">
         <v>45784</v>
       </c>
-      <c r="F51">
+      <c r="G51">
         <f>INT((Recueil[[#This Row],[Date_de_recueil]]-Recueil[[#This Row],[DDN]])/365)</f>
         <v>72</v>
       </c>
-      <c r="G51" t="s">
+      <c r="H51" t="s">
         <v>16</v>
       </c>
-      <c r="I51" t="s">
-        <v>8</v>
-      </c>
       <c r="J51" t="s">
         <v>8</v>
       </c>
-      <c r="M51" t="s">
+      <c r="K51" t="s">
         <v>8</v>
       </c>
       <c r="N51" t="s">
@@ -4241,7 +4401,7 @@
       <c r="R51" t="s">
         <v>8</v>
       </c>
-      <c r="T51" t="s">
+      <c r="S51" t="s">
         <v>8</v>
       </c>
       <c r="U51" t="s">
@@ -4256,8 +4416,11 @@
       <c r="X51" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="52" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Y51" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="52" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>51</v>
       </c>
@@ -4267,57 +4430,60 @@
       <c r="C52" t="s">
         <v>113</v>
       </c>
-      <c r="D52" s="1">
+      <c r="D52" t="s">
+        <v>139</v>
+      </c>
+      <c r="E52" s="1">
         <v>23968</v>
       </c>
-      <c r="E52" s="1">
+      <c r="F52" s="1">
         <v>45838</v>
       </c>
-      <c r="F52">
+      <c r="G52">
         <f>INT((Recueil[[#This Row],[Date_de_recueil]]-Recueil[[#This Row],[DDN]])/365)</f>
         <v>59</v>
-      </c>
-      <c r="I52" t="s">
-        <v>3</v>
       </c>
       <c r="J52" t="s">
         <v>3</v>
       </c>
-      <c r="M52" t="s">
+      <c r="K52" t="s">
         <v>3</v>
       </c>
       <c r="N52" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O52" t="s">
         <v>7</v>
       </c>
       <c r="P52" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q52" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R52" t="s">
-        <v>8</v>
-      </c>
-      <c r="T52" t="s">
-        <v>7</v>
+        <v>7</v>
+      </c>
+      <c r="S52" t="s">
+        <v>8</v>
       </c>
       <c r="U52" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V52" t="s">
         <v>8</v>
       </c>
       <c r="W52" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X52" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="53" spans="1:25" x14ac:dyDescent="0.2">
+        <v>7</v>
+      </c>
+      <c r="Y52" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>52</v>
       </c>
@@ -4327,23 +4493,23 @@
       <c r="C53" t="s">
         <v>115</v>
       </c>
-      <c r="D53" s="1">
+      <c r="D53" t="s">
+        <v>139</v>
+      </c>
+      <c r="E53" s="1">
         <v>24826</v>
       </c>
-      <c r="E53" s="1">
+      <c r="F53" s="1">
         <v>45838</v>
       </c>
-      <c r="F53">
+      <c r="G53">
         <f>INT((Recueil[[#This Row],[Date_de_recueil]]-Recueil[[#This Row],[DDN]])/365)</f>
         <v>57</v>
       </c>
-      <c r="I53" t="s">
-        <v>7</v>
-      </c>
       <c r="J53" t="s">
         <v>7</v>
       </c>
-      <c r="M53" t="s">
+      <c r="K53" t="s">
         <v>7</v>
       </c>
       <c r="N53" t="s">
@@ -4359,10 +4525,10 @@
         <v>7</v>
       </c>
       <c r="R53" t="s">
-        <v>8</v>
-      </c>
-      <c r="T53" t="s">
-        <v>7</v>
+        <v>7</v>
+      </c>
+      <c r="S53" t="s">
+        <v>8</v>
       </c>
       <c r="U53" t="s">
         <v>7</v>
@@ -4374,10 +4540,13 @@
         <v>7</v>
       </c>
       <c r="X53" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="54" spans="1:25" x14ac:dyDescent="0.2">
+        <v>7</v>
+      </c>
+      <c r="Y53" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="54" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>53</v>
       </c>
@@ -4387,23 +4556,23 @@
       <c r="C54" t="s">
         <v>117</v>
       </c>
-      <c r="D54" s="1">
+      <c r="D54" t="s">
+        <v>138</v>
+      </c>
+      <c r="E54" s="1">
         <v>27395</v>
       </c>
-      <c r="E54" s="1">
+      <c r="F54" s="1">
         <v>45810</v>
       </c>
-      <c r="F54">
+      <c r="G54">
         <f>INT((Recueil[[#This Row],[Date_de_recueil]]-Recueil[[#This Row],[DDN]])/365)</f>
         <v>50</v>
       </c>
-      <c r="I54" t="s">
-        <v>8</v>
-      </c>
       <c r="J54" t="s">
         <v>8</v>
       </c>
-      <c r="M54" t="s">
+      <c r="K54" t="s">
         <v>8</v>
       </c>
       <c r="N54" t="s">
@@ -4421,14 +4590,14 @@
       <c r="R54" t="s">
         <v>8</v>
       </c>
-      <c r="T54" t="s">
+      <c r="S54" t="s">
         <v>8</v>
       </c>
       <c r="U54" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V54" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W54" t="s">
         <v>8</v>
@@ -4436,8 +4605,11 @@
       <c r="X54" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="55" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Y54" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>54</v>
       </c>
@@ -4447,16 +4619,25 @@
       <c r="C55" t="s">
         <v>119</v>
       </c>
-      <c r="D55" s="1">
+      <c r="D55" t="s">
+        <v>138</v>
+      </c>
+      <c r="E55" s="1">
         <v>23919</v>
       </c>
-      <c r="E55" s="1">
+      <c r="F55" s="1">
         <v>45775</v>
       </c>
-      <c r="F55">
+      <c r="G55">
         <f>INT((Recueil[[#This Row],[Date_de_recueil]]-Recueil[[#This Row],[DDN]])/365)</f>
         <v>59</v>
       </c>
+      <c r="J55" t="s">
+        <v>7</v>
+      </c>
+      <c r="K55" t="s">
+        <v>7</v>
+      </c>
       <c r="N55" t="s">
         <v>7</v>
       </c>
@@ -4473,35 +4654,38 @@
         <v>7</v>
       </c>
       <c r="S55" t="s">
+        <v>7</v>
+      </c>
+      <c r="T55" t="s">
         <v>25</v>
       </c>
-      <c r="T55" t="s">
-        <v>8</v>
-      </c>
       <c r="U55" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V55" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W55" t="s">
         <v>8</v>
       </c>
       <c r="X55" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y55" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z55" t="s">
         <v>25</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D55" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E55" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>1</formula1>
       <formula2>44197</formula2>
     </dataValidation>
-    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E1048576" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F1048576" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>1</formula1>
       <formula2>47484</formula2>
     </dataValidation>
@@ -4518,43 +4702,43 @@
           <x14:formula1>
             <xm:f>Feuil1!$R$9:$R$11</xm:f>
           </x14:formula1>
-          <xm:sqref>M2:M55 L56:L1048576 I2:J1048576</xm:sqref>
+          <xm:sqref>N2:N55 M56:M1048576 J2:K1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000004000000}">
           <x14:formula1>
             <xm:f>Feuil1!$R$3:$R$4</xm:f>
           </x14:formula1>
-          <xm:sqref>K2:K55</xm:sqref>
+          <xm:sqref>L2:L55</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000005000000}">
           <x14:formula1>
             <xm:f>Feuil1!$R$9:$R$10</xm:f>
           </x14:formula1>
-          <xm:sqref>K56:K1048576 L2:L55</xm:sqref>
+          <xm:sqref>L56:L1048576 M2:M55</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000006000000}">
           <x14:formula1>
             <xm:f>Feuil1!$S$5:$S$7</xm:f>
           </x14:formula1>
-          <xm:sqref>S56:W1048576 T2:X55 M56:Q1048576 N2:R55</xm:sqref>
+          <xm:sqref>T56:X1048576 U2:Y55 N56:R1048576 O2:S55</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000007000000}">
           <x14:formula1>
             <xm:f>Feuil1!$U$5:$U$7</xm:f>
           </x14:formula1>
-          <xm:sqref>R56:R1048576 S2:S55 X56:X1048576 Y2:Y55</xm:sqref>
+          <xm:sqref>S56:S1048576 T2:T55 Y56:Y1048576 Z2:Z55</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000008000000}">
           <x14:formula1>
             <xm:f>Feuil1!$O$13:$O$20</xm:f>
           </x14:formula1>
-          <xm:sqref>H2:H55</xm:sqref>
+          <xm:sqref>I2:I55</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000002000000}">
           <x14:formula1>
             <xm:f>Feuil1!$R$7:$R$8</xm:f>
           </x14:formula1>
-          <xm:sqref>G2:G1048576</xm:sqref>
+          <xm:sqref>H2:H1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/recueil_bon.xlsx
+++ b/recueil_bon.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10503"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10703"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/thomashusson/Documents/Projets/These_Brieuc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9E934CC-B85E-5045-AD07-6545741DF615}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63DDBB44-C6F1-514D-A3AE-1EFD744198B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -907,7 +907,7 @@
     <col min="7" max="7" width="15.1640625" customWidth="1"/>
     <col min="8" max="8" width="11.5" customWidth="1"/>
     <col min="9" max="10" width="16.5" customWidth="1"/>
-    <col min="11" max="11" width="11.5" customWidth="1"/>
+    <col min="11" max="11" width="22.1640625" customWidth="1"/>
     <col min="12" max="16" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
